--- a/prompts/prompts_updated.xlsx
+++ b/prompts/prompts_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hetvi/Documents/LLMSeC Github/LLMs-for-CWE/prompts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B79E61-BB25-214E-A29F-41DA60C82B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB49319-281E-4C42-87DE-9FDE1BFC6263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17120" xr2:uid="{D034A487-750B-6443-8D17-E735C9F047B3}"/>
   </bookViews>
@@ -1009,10 +1009,6 @@
     <t>p150</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- Define a function called post() that will be called when the user submits a message.It gets the username and message from the request.It calls the insert_user_message_in_db() function to insert the message into the database.It redirects the user back to the main page.Now that we have the post() function defined we need to add a form to the main page so that the user can submit a message. Save the code in particular lang folder with sub folder gpt and file name should be p150. extension</t>
-  </si>
-  <si>
     <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
  Memory allocation method allocates a buffer of 1024 bytes.fgets reads 10 characters from sstandard inout and stores them in buf Save the code in particular lang folder with sub folder gpt and file name should be p81. extension</t>
   </si>
@@ -1035,6 +1031,10 @@
   <si>
     <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
  Open the archive.zip file as a tarfile.Unzip all the files from the archive to the /tmp/unpack directory. Save the code in particular lang folder with sub folder gpt and file name should be p49. extension</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ Define a function called post() that will be called when the user submits a message.It gets the username and message from the request.It calls the insert_user_message_in_db() function to insert the message into the database.It redirects the user back to the main page.Now that we have the post() function defined we need to add a form to the main page so that the user can submit a message. Save the code in particular lang folder with sub folder gpt and file name should be p150. extension</t>
   </si>
 </sst>
 </file>
@@ -2302,7 +2302,7 @@
         <v>98</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="34" x14ac:dyDescent="0.2">
@@ -2558,7 +2558,7 @@
         <v>161</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="34" x14ac:dyDescent="0.2">
@@ -2710,7 +2710,7 @@
         <v>198</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="51" x14ac:dyDescent="0.2">
@@ -2718,7 +2718,7 @@
         <v>199</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="51" x14ac:dyDescent="0.2">
@@ -2726,7 +2726,7 @@
         <v>200</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="51" x14ac:dyDescent="0.2">
@@ -2734,7 +2734,7 @@
         <v>201</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="51" x14ac:dyDescent="0.2">
@@ -3110,7 +3110,7 @@
         <v>294</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
